--- a/relatorios/premiacao/Premiacao_SDR_JUNHO_JULHO_2026.xlsx
+++ b/relatorios/premiacao/Premiacao_SDR_JUNHO_JULHO_2026.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="375">
   <si>
     <t>PREMIAÇÃO SDR — GRUPO VIGNA — 22/06 → 17/07/2026</t>
   </si>
@@ -347,6 +347,54 @@
     <t>(sem negócios no período)</t>
   </si>
   <si>
+    <t>ANA KAROLAYNE  (&lt;1 ano)</t>
+  </si>
+  <si>
+    <t>ACOS FORMOSA COMERCIAL E INDUSTRIAL LTDA</t>
+  </si>
+  <si>
+    <t>lucro</t>
+  </si>
+  <si>
+    <t>https://beta.agendor.com.br/tasks?organizationId=543408</t>
+  </si>
+  <si>
+    <t>AMIGOO PET SERVICOS DE ASSISTENCIA</t>
+  </si>
+  <si>
+    <t>DIAGNÓSTICO - REFORMA TRIBUTÁRIA</t>
+  </si>
+  <si>
+    <t>https://beta.agendor.com.br/tasks?organizationId=31298439</t>
+  </si>
+  <si>
+    <t>TOTAL: 2 fechamento(s)</t>
+  </si>
+  <si>
+    <t>IGOR  (&lt;1 ano)</t>
+  </si>
+  <si>
+    <t>LARISSA  (&lt;1 ano)</t>
+  </si>
+  <si>
+    <t>ANA BELLE  (&lt;1 ano)</t>
+  </si>
+  <si>
+    <t>23/06/2026</t>
+  </si>
+  <si>
+    <t>LUCIANE INDUSTRIA MOVELEIRA LTDA</t>
+  </si>
+  <si>
+    <t>CANAL DE DENUNCIA,COMPLIANCE NR1+</t>
+  </si>
+  <si>
+    <t>https://beta.agendor.com.br/tasks?organizationId=46471275</t>
+  </si>
+  <si>
+    <t>LETICIA  (+1 ano)</t>
+  </si>
+  <si>
     <t>ANA BEATRIZ  (+1 ano)</t>
   </si>
   <si>
@@ -368,12 +416,12 @@
     <t>https://beta.agendor.com.br/tasks?organizationId=52279439</t>
   </si>
   <si>
-    <t>TOTAL: 2 fechamento(s)</t>
-  </si>
-  <si>
     <t>LAWANNY  (&lt;1 ano)</t>
   </si>
   <si>
+    <t>RAILANNE  (&lt;1 ano)</t>
+  </si>
+  <si>
     <t>IGOR VASCONCELOS  (&lt;1 ano)</t>
   </si>
   <si>
@@ -486,9 +534,6 @@
   </si>
   <si>
     <t>NOVA VC: R$7,50 | NOVA Presencial: R$15 | FUP VC: R$5 | FUP Presencial: R$7,50</t>
-  </si>
-  <si>
-    <t>23/06/2026</t>
   </si>
   <si>
     <t>PELICANO CONSTRUCOES S.A.</t>
@@ -1908,16 +1953,16 @@
         <v>105</v>
       </c>
       <c r="G9" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I9" s="5">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J9" s="7">
-        <v>105</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1972,16 +2017,16 @@
         <v>287.5</v>
       </c>
       <c r="G11">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H11" t="s">
         <v>1</v>
       </c>
       <c r="I11" s="7">
-        <v>1810</v>
+        <v>2010</v>
       </c>
       <c r="J11" s="7">
-        <v>2097.5</v>
+        <v>2297.5</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2084,16 +2129,16 @@
         <v>57.5</v>
       </c>
       <c r="G16" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I16" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J16" s="7">
-        <v>57.5</v>
+        <v>157.5</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2244,16 +2289,16 @@
         <v>530</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21" t="s">
         <v>1</v>
       </c>
       <c r="I21" s="7">
-        <v>240</v>
+        <v>340</v>
       </c>
       <c r="J21" s="7">
-        <v>770</v>
+        <v>870</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -2317,7 +2362,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="13">
-        <v>3367.5</v>
+        <v>3667.5</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -2619,7 +2664,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="38"/>
@@ -2633,24 +2678,24 @@
         <v>1</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>59</v>
@@ -2664,199 +2709,199 @@
         <v>1</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
-        <v>154</v>
+        <v>118</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="C6" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F6" s="34">
         <f>=IF(AND(D6="NOVA",E6="PRESENCIAL"),15,IF(AND(D6="FUP",E6="PRESENCIAL"),7.5,IF(D6="NOVA",7.5,IF(D6="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
-        <v>154</v>
+        <v>118</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="C7" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F7" s="34">
         <f>=IF(AND(D7="NOVA",E7="PRESENCIAL"),15,IF(AND(D7="FUP",E7="PRESENCIAL"),7.5,IF(D7="NOVA",7.5,IF(D7="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="C8" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F8" s="34">
         <f>=IF(AND(D8="NOVA",E8="PRESENCIAL"),15,IF(AND(D8="FUP",E8="PRESENCIAL"),7.5,IF(D8="NOVA",7.5,IF(D8="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="33" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="C9" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F9" s="34">
         <f>=IF(AND(D9="NOVA",E9="PRESENCIAL"),15,IF(AND(D9="FUP",E9="PRESENCIAL"),7.5,IF(D9="NOVA",7.5,IF(D9="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="C10" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F10" s="34">
         <f>=IF(AND(D10="NOVA",E10="PRESENCIAL"),15,IF(AND(D10="FUP",E10="PRESENCIAL"),7.5,IF(D10="NOVA",7.5,IF(D10="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G10" s="33" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="40" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="C11" s="40" t="s">
         <v>1</v>
       </c>
       <c r="D11" s="41" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="E11" s="41" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F11" s="42">
         <f>=IF(AND(D11="NOVA",E11="PRESENCIAL"),15,IF(AND(D11="FUP",E11="PRESENCIAL"),7.5,IF(D11="NOVA",7.5,IF(D11="FUP",5,0))))</f>
         <v>5</v>
       </c>
       <c r="G11" s="40" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="33" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="C12" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F12" s="34">
         <f>=IF(AND(D12="NOVA",E12="PRESENCIAL"),15,IF(AND(D12="FUP",E12="PRESENCIAL"),7.5,IF(D12="NOVA",7.5,IF(D12="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G12" s="33" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="33" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="C13" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F13" s="34">
         <f>=IF(AND(D13="NOVA",E13="PRESENCIAL"),15,IF(AND(D13="FUP",E13="PRESENCIAL"),7.5,IF(D13="NOVA",7.5,IF(D13="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G13" s="33" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2864,13 +2909,13 @@
         <v>1</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="C15" t="s">
         <v>1</v>
       </c>
       <c r="D15" s="43" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="E15" t="s">
         <v>1</v>
@@ -2919,7 +2964,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="38"/>
@@ -2933,24 +2978,24 @@
         <v>1</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>59</v>
@@ -2964,7 +3009,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -2972,23 +3017,23 @@
         <v>70</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="C6" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F6" s="34">
         <f>=IF(AND(D6="NOVA",E6="PRESENCIAL"),25,IF(AND(D6="FUP",E6="PRESENCIAL"),10,IF(D6="NOVA",10,IF(D6="FUP",5,0))))</f>
         <v>10</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -2996,23 +3041,23 @@
         <v>70</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="C7" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F7" s="34">
         <f>=IF(AND(D7="NOVA",E7="PRESENCIAL"),25,IF(AND(D7="FUP",E7="PRESENCIAL"),10,IF(D7="NOVA",10,IF(D7="FUP",5,0))))</f>
         <v>10</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -3020,13 +3065,13 @@
         <v>1</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="C9" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="43" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="E9" t="s">
         <v>1</v>
@@ -3069,7 +3114,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="38"/>
@@ -3083,24 +3128,24 @@
         <v>1</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>59</v>
@@ -3114,55 +3159,55 @@
         <v>1</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
-        <v>154</v>
+        <v>118</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="C6" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F6" s="34">
         <f>=IF(AND(D6="NOVA",E6="PRESENCIAL"),25,IF(AND(D6="FUP",E6="PRESENCIAL"),10,IF(D6="NOVA",10,IF(D6="FUP",5,0))))</f>
         <v>10</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="C7" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F7" s="34">
         <f>=IF(AND(D7="NOVA",E7="PRESENCIAL"),25,IF(AND(D7="FUP",E7="PRESENCIAL"),10,IF(D7="NOVA",10,IF(D7="FUP",5,0))))</f>
         <v>10</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -3170,143 +3215,143 @@
         <v>92</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="C8" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F8" s="34">
         <f>=IF(AND(D8="NOVA",E8="PRESENCIAL"),25,IF(AND(D8="FUP",E8="PRESENCIAL"),10,IF(D8="NOVA",10,IF(D8="FUP",5,0))))</f>
         <v>10</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="33" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="C9" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F9" s="34">
         <f>=IF(AND(D9="NOVA",E9="PRESENCIAL"),25,IF(AND(D9="FUP",E9="PRESENCIAL"),10,IF(D9="NOVA",10,IF(D9="FUP",5,0))))</f>
         <v>10</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="C10" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F10" s="34">
         <f>=IF(AND(D10="NOVA",E10="PRESENCIAL"),25,IF(AND(D10="FUP",E10="PRESENCIAL"),10,IF(D10="NOVA",10,IF(D10="FUP",5,0))))</f>
         <v>10</v>
       </c>
       <c r="G10" s="33" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="C11" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F11" s="34">
         <f>=IF(AND(D11="NOVA",E11="PRESENCIAL"),25,IF(AND(D11="FUP",E11="PRESENCIAL"),10,IF(D11="NOVA",10,IF(D11="FUP",5,0))))</f>
         <v>10</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="33" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="C12" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F12" s="34">
         <f>=IF(AND(D12="NOVA",E12="PRESENCIAL"),25,IF(AND(D12="FUP",E12="PRESENCIAL"),10,IF(D12="NOVA",10,IF(D12="FUP",5,0))))</f>
         <v>10</v>
       </c>
       <c r="G12" s="33" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="33" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="C13" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F13" s="34">
         <f>=IF(AND(D13="NOVA",E13="PRESENCIAL"),25,IF(AND(D13="FUP",E13="PRESENCIAL"),10,IF(D13="NOVA",10,IF(D13="FUP",5,0))))</f>
         <v>10</v>
       </c>
       <c r="G13" s="33" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -3314,23 +3359,23 @@
         <v>82</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="C14" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F14" s="34">
         <f>=IF(AND(D14="NOVA",E14="PRESENCIAL"),25,IF(AND(D14="FUP",E14="PRESENCIAL"),10,IF(D14="NOVA",10,IF(D14="FUP",5,0))))</f>
         <v>10</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -3338,23 +3383,23 @@
         <v>82</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="C15" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F15" s="34">
         <f>=IF(AND(D15="NOVA",E15="PRESENCIAL"),25,IF(AND(D15="FUP",E15="PRESENCIAL"),10,IF(D15="NOVA",10,IF(D15="FUP",5,0))))</f>
         <v>10</v>
       </c>
       <c r="G15" s="33" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -3362,71 +3407,71 @@
         <v>82</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="C16" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F16" s="34">
         <f>=IF(AND(D16="NOVA",E16="PRESENCIAL"),25,IF(AND(D16="FUP",E16="PRESENCIAL"),10,IF(D16="NOVA",10,IF(D16="FUP",5,0))))</f>
         <v>10</v>
       </c>
       <c r="G16" s="33" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="33" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C17" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E17" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F17" s="34">
         <f>=IF(AND(D17="NOVA",E17="PRESENCIAL"),25,IF(AND(D17="FUP",E17="PRESENCIAL"),10,IF(D17="NOVA",10,IF(D17="FUP",5,0))))</f>
         <v>10</v>
       </c>
       <c r="G17" s="33" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="33" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="C18" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F18" s="34">
         <f>=IF(AND(D18="NOVA",E18="PRESENCIAL"),25,IF(AND(D18="FUP",E18="PRESENCIAL"),10,IF(D18="NOVA",10,IF(D18="FUP",5,0))))</f>
         <v>10</v>
       </c>
       <c r="G18" s="33" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -3434,119 +3479,119 @@
         <v>65</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="C19" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F19" s="34">
         <f>=IF(AND(D19="NOVA",E19="PRESENCIAL"),25,IF(AND(D19="FUP",E19="PRESENCIAL"),10,IF(D19="NOVA",10,IF(D19="FUP",5,0))))</f>
         <v>10</v>
       </c>
       <c r="G19" s="33" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="33" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="B20" s="33" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="C20" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F20" s="34">
         <f>=IF(AND(D20="NOVA",E20="PRESENCIAL"),25,IF(AND(D20="FUP",E20="PRESENCIAL"),10,IF(D20="NOVA",10,IF(D20="FUP",5,0))))</f>
         <v>10</v>
       </c>
       <c r="G20" s="33" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="40" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="C21" s="40" t="s">
         <v>1</v>
       </c>
       <c r="D21" s="41" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F21" s="42">
         <f>=IF(AND(D21="NOVA",E21="PRESENCIAL"),25,IF(AND(D21="FUP",E21="PRESENCIAL"),10,IF(D21="NOVA",10,IF(D21="FUP",5,0))))</f>
         <v>5</v>
       </c>
       <c r="G21" s="40" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="40" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="B22" s="40" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="C22" s="40" t="s">
         <v>1</v>
       </c>
       <c r="D22" s="41" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F22" s="42">
         <f>=IF(AND(D22="NOVA",E22="PRESENCIAL"),25,IF(AND(D22="FUP",E22="PRESENCIAL"),10,IF(D22="NOVA",10,IF(D22="FUP",5,0))))</f>
         <v>5</v>
       </c>
       <c r="G22" s="40" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="33" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="C23" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D23" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E23" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F23" s="34">
         <f>=IF(AND(D23="NOVA",E23="PRESENCIAL"),25,IF(AND(D23="FUP",E23="PRESENCIAL"),10,IF(D23="NOVA",10,IF(D23="FUP",5,0))))</f>
         <v>10</v>
       </c>
       <c r="G23" s="33" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -3554,13 +3599,13 @@
         <v>1</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="C25" t="s">
         <v>1</v>
       </c>
       <c r="D25" s="43" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="E25" t="s">
         <v>1</v>
@@ -3609,7 +3654,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="38"/>
@@ -3623,24 +3668,24 @@
         <v>1</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>59</v>
@@ -3654,79 +3699,79 @@
         <v>1</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
-        <v>154</v>
+        <v>118</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="C6" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F6" s="34">
         <f>=IF(AND(D6="NOVA",E6="PRESENCIAL"),15,IF(AND(D6="FUP",E6="PRESENCIAL"),7.5,IF(D6="NOVA",7.5,IF(D6="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="C7" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F7" s="34">
         <f>=IF(AND(D7="NOVA",E7="PRESENCIAL"),15,IF(AND(D7="FUP",E7="PRESENCIAL"),7.5,IF(D7="NOVA",7.5,IF(D7="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="C8" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F8" s="34">
         <f>=IF(AND(D8="NOVA",E8="PRESENCIAL"),15,IF(AND(D8="FUP",E8="PRESENCIAL"),7.5,IF(D8="NOVA",7.5,IF(D8="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -3734,47 +3779,47 @@
         <v>92</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="C9" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F9" s="34">
         <f>=IF(AND(D9="NOVA",E9="PRESENCIAL"),15,IF(AND(D9="FUP",E9="PRESENCIAL"),7.5,IF(D9="NOVA",7.5,IF(D9="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="C10" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F10" s="34">
         <f>=IF(AND(D10="NOVA",E10="PRESENCIAL"),15,IF(AND(D10="FUP",E10="PRESENCIAL"),7.5,IF(D10="NOVA",7.5,IF(D10="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G10" s="33" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -3782,47 +3827,47 @@
         <v>82</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="C11" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F11" s="34">
         <f>=IF(AND(D11="NOVA",E11="PRESENCIAL"),15,IF(AND(D11="FUP",E11="PRESENCIAL"),7.5,IF(D11="NOVA",7.5,IF(D11="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="33" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="C12" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F12" s="34">
         <f>=IF(AND(D12="NOVA",E12="PRESENCIAL"),15,IF(AND(D12="FUP",E12="PRESENCIAL"),7.5,IF(D12="NOVA",7.5,IF(D12="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G12" s="33" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -3830,47 +3875,47 @@
         <v>65</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="C13" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F13" s="34">
         <f>=IF(AND(D13="NOVA",E13="PRESENCIAL"),15,IF(AND(D13="FUP",E13="PRESENCIAL"),7.5,IF(D13="NOVA",7.5,IF(D13="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G13" s="33" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="C14" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F14" s="34">
         <f>=IF(AND(D14="NOVA",E14="PRESENCIAL"),15,IF(AND(D14="FUP",E14="PRESENCIAL"),7.5,IF(D14="NOVA",7.5,IF(D14="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -3878,47 +3923,47 @@
         <v>61</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="C15" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F15" s="34">
         <f>=IF(AND(D15="NOVA",E15="PRESENCIAL"),15,IF(AND(D15="FUP",E15="PRESENCIAL"),7.5,IF(D15="NOVA",7.5,IF(D15="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G15" s="33" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="33" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="C16" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F16" s="34">
         <f>=IF(AND(D16="NOVA",E16="PRESENCIAL"),15,IF(AND(D16="FUP",E16="PRESENCIAL"),7.5,IF(D16="NOVA",7.5,IF(D16="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G16" s="33" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -3926,13 +3971,13 @@
         <v>1</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="C18" t="s">
         <v>1</v>
       </c>
       <c r="D18" s="43" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="E18" t="s">
         <v>1</v>
@@ -3981,7 +4026,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="38"/>
@@ -3995,24 +4040,24 @@
         <v>1</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>59</v>
@@ -4026,175 +4071,175 @@
         <v>1</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="C6" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F6" s="34">
         <f>=IF(AND(D6="NOVA",E6="PRESENCIAL"),15,IF(AND(D6="FUP",E6="PRESENCIAL"),7.5,IF(D6="NOVA",7.5,IF(D6="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="C7" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F7" s="34">
         <f>=IF(AND(D7="NOVA",E7="PRESENCIAL"),15,IF(AND(D7="FUP",E7="PRESENCIAL"),7.5,IF(D7="NOVA",7.5,IF(D7="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C8" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F8" s="34">
         <f>=IF(AND(D8="NOVA",E8="PRESENCIAL"),15,IF(AND(D8="FUP",E8="PRESENCIAL"),7.5,IF(D8="NOVA",7.5,IF(D8="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="33" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="C9" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F9" s="34">
         <f>=IF(AND(D9="NOVA",E9="PRESENCIAL"),15,IF(AND(D9="FUP",E9="PRESENCIAL"),7.5,IF(D9="NOVA",7.5,IF(D9="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="C10" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F10" s="34">
         <f>=IF(AND(D10="NOVA",E10="PRESENCIAL"),15,IF(AND(D10="FUP",E10="PRESENCIAL"),7.5,IF(D10="NOVA",7.5,IF(D10="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G10" s="33" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="C11" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F11" s="34">
         <f>=IF(AND(D11="NOVA",E11="PRESENCIAL"),15,IF(AND(D11="FUP",E11="PRESENCIAL"),7.5,IF(D11="NOVA",7.5,IF(D11="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="33" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="C12" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F12" s="34">
         <f>=IF(AND(D12="NOVA",E12="PRESENCIAL"),15,IF(AND(D12="FUP",E12="PRESENCIAL"),7.5,IF(D12="NOVA",7.5,IF(D12="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G12" s="33" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4202,23 +4247,23 @@
         <v>74</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="C13" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F13" s="34">
         <f>=IF(AND(D13="NOVA",E13="PRESENCIAL"),15,IF(AND(D13="FUP",E13="PRESENCIAL"),7.5,IF(D13="NOVA",7.5,IF(D13="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G13" s="33" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4226,23 +4271,23 @@
         <v>65</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="C14" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F14" s="34">
         <f>=IF(AND(D14="NOVA",E14="PRESENCIAL"),15,IF(AND(D14="FUP",E14="PRESENCIAL"),7.5,IF(D14="NOVA",7.5,IF(D14="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>349</v>
+        <v>364</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4250,23 +4295,23 @@
         <v>61</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>350</v>
+        <v>365</v>
       </c>
       <c r="C15" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F15" s="34">
         <f>=IF(AND(D15="NOVA",E15="PRESENCIAL"),15,IF(AND(D15="FUP",E15="PRESENCIAL"),7.5,IF(D15="NOVA",7.5,IF(D15="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G15" s="33" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4274,95 +4319,95 @@
         <v>61</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="C16" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F16" s="34">
         <f>=IF(AND(D16="NOVA",E16="PRESENCIAL"),15,IF(AND(D16="FUP",E16="PRESENCIAL"),7.5,IF(D16="NOVA",7.5,IF(D16="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G16" s="33" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="33" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="C17" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E17" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F17" s="34">
         <f>=IF(AND(D17="NOVA",E17="PRESENCIAL"),15,IF(AND(D17="FUP",E17="PRESENCIAL"),7.5,IF(D17="NOVA",7.5,IF(D17="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G17" s="33" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="33" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="C18" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F18" s="34">
         <f>=IF(AND(D18="NOVA",E18="PRESENCIAL"),15,IF(AND(D18="FUP",E18="PRESENCIAL"),7.5,IF(D18="NOVA",7.5,IF(D18="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G18" s="33" t="s">
-        <v>357</v>
+        <v>372</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="33" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="C19" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F19" s="34">
         <f>=IF(AND(D19="NOVA",E19="PRESENCIAL"),15,IF(AND(D19="FUP",E19="PRESENCIAL"),7.5,IF(D19="NOVA",7.5,IF(D19="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G19" s="33" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -4370,13 +4415,13 @@
         <v>1</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="C21" t="s">
         <v>1</v>
       </c>
       <c r="D21" s="43" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="E21" t="s">
         <v>1</v>
@@ -4411,7 +4456,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -4838,7 +4883,7 @@
         <v>1</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -4859,38 +4904,38 @@
       </c>
     </row>
     <row r="36" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="B36" s="23" t="s">
+      <c r="C36" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="C36" s="23" t="s">
+      <c r="D36" s="34">
+        <f>=100</f>
+        <v>100</v>
+      </c>
+      <c r="E36" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="D36" s="24">
-        <f>=IF(ROW()-36+1&lt;=5,120,IF(ROW()-36+1&lt;=10,150,180))</f>
-        <v>120</v>
-      </c>
-      <c r="E36" s="23" t="s">
+    </row>
+    <row r="37" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="33" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="37" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="B37" s="23" t="s">
+      <c r="C37" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="C37" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D37" s="24">
-        <f>=IF(ROW()-36+1&lt;=5,120,IF(ROW()-36+1&lt;=10,150,180))</f>
-        <v>120</v>
-      </c>
-      <c r="E37" s="23" t="s">
+      <c r="D37" s="34">
+        <f>=100</f>
+        <v>100</v>
+      </c>
+      <c r="E37" s="33" t="s">
         <v>113</v>
       </c>
     </row>
@@ -4906,7 +4951,7 @@
       </c>
       <c r="D38" s="31">
         <f>=SUM(D36:D37)</f>
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="E38" t="s">
         <v>1</v>
@@ -4988,133 +5033,459 @@
         <v>60</v>
       </c>
     </row>
-    <row r="48" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="32" t="s">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>1</v>
+      </c>
+      <c r="B48" s="35" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="B48" s="33" t="s">
-        <v>101</v>
-      </c>
-      <c r="C48" s="33" t="s">
+      <c r="B50" s="19"/>
+      <c r="C50" s="19"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="19"/>
+    </row>
+    <row r="51" ht="13" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B51" s="20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C52" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D52" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="E52" s="21" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="D48" s="34">
+      <c r="B53" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="C53" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="D53" s="34">
         <f>=100</f>
         <v>100</v>
       </c>
-      <c r="E48" s="33" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="49" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="32" t="s">
+      <c r="E53" s="33" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>1</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1</v>
+      </c>
+      <c r="D54" s="31">
+        <f>=SUM(D53:D53)</f>
+        <v>100</v>
+      </c>
+      <c r="E54" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B56" s="19"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="19"/>
+    </row>
+    <row r="57" ht="13" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>1</v>
+      </c>
+      <c r="B57" s="20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B58" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C58" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D58" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="E58" s="21" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>1</v>
+      </c>
+      <c r="B59" s="35" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="B61" s="19"/>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+    </row>
+    <row r="62" ht="13" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>1</v>
+      </c>
+      <c r="B62" s="20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B63" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C63" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D63" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="E63" s="21" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="B64" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="C64" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="D64" s="24">
+        <f>=IF(ROW()-64+1&lt;=5,120,IF(ROW()-64+1&lt;=10,150,180))</f>
+        <v>120</v>
+      </c>
+      <c r="E64" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="B49" s="33" t="s">
+      <c r="B65" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="C65" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="D65" s="24">
+        <f>=IF(ROW()-64+1&lt;=5,120,IF(ROW()-64+1&lt;=10,150,180))</f>
+        <v>120</v>
+      </c>
+      <c r="E65" s="23" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>1</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1</v>
+      </c>
+      <c r="D66" s="31">
+        <f>=SUM(D64:D65)</f>
+        <v>240</v>
+      </c>
+      <c r="E66" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="B68" s="19"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="19"/>
+      <c r="E68" s="19"/>
+    </row>
+    <row r="69" ht="13" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>1</v>
+      </c>
+      <c r="B69" s="20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B70" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C70" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D70" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="E70" s="21" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>1</v>
+      </c>
+      <c r="B71" s="35" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B73" s="19"/>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+    </row>
+    <row r="74" ht="13" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>1</v>
+      </c>
+      <c r="B74" s="20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B75" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D75" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="E75" s="21" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>1</v>
+      </c>
+      <c r="B76" s="35" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="B78" s="19"/>
+      <c r="C78" s="19"/>
+      <c r="D78" s="19"/>
+      <c r="E78" s="19"/>
+    </row>
+    <row r="79" ht="13" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>1</v>
+      </c>
+      <c r="B79" s="20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B80" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C80" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D80" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="E80" s="21" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="B81" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="C49" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="D49" s="34">
+      <c r="C81" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="D81" s="34">
         <f>=100</f>
         <v>100</v>
       </c>
-      <c r="E49" s="33" t="s">
+      <c r="E81" s="33" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="50" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="B50" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="C50" s="33" t="s">
-        <v>121</v>
-      </c>
-      <c r="D50" s="34">
+    <row r="82" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="B82" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="C82" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="D82" s="34">
         <f>=100</f>
         <v>100</v>
       </c>
-      <c r="E50" s="33" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="51" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="B51" s="33" t="s">
-        <v>123</v>
-      </c>
-      <c r="C51" s="33" t="s">
-        <v>110</v>
-      </c>
-      <c r="D51" s="34">
+      <c r="E82" s="33" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="B83" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="C83" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="D83" s="34">
         <f>=100</f>
         <v>100</v>
       </c>
-      <c r="E51" s="33" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="52" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="32" t="s">
-        <v>92</v>
-      </c>
-      <c r="B52" s="33" t="s">
-        <v>125</v>
-      </c>
-      <c r="C52" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="D52" s="34">
+      <c r="E83" s="33" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="B84" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="C84" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="D84" s="34">
         <f>=100</f>
         <v>100</v>
       </c>
-      <c r="E52" s="33" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>1</v>
-      </c>
-      <c r="B53" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="C53" t="s">
-        <v>1</v>
-      </c>
-      <c r="D53" s="31">
-        <f>=SUM(D48:D52)</f>
+      <c r="E84" s="33" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="B85" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="C85" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="D85" s="34">
+        <f>=100</f>
+        <v>100</v>
+      </c>
+      <c r="E85" s="33" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>1</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1</v>
+      </c>
+      <c r="D86" s="31">
+        <f>=SUM(D81:D85)</f>
         <v>500</v>
       </c>
-      <c r="E53" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>1</v>
-      </c>
-      <c r="B56" s="36" t="s">
-        <v>128</v>
-      </c>
-      <c r="C56" t="s">
-        <v>1</v>
-      </c>
-      <c r="D56" s="37">
-        <v>2550</v>
-      </c>
-      <c r="E56" t="s">
+      <c r="E86" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>1</v>
+      </c>
+      <c r="B89" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="C89" t="s">
+        <v>1</v>
+      </c>
+      <c r="D89" s="37">
+        <v>2850</v>
+      </c>
+      <c r="E89" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="13">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A22:E22"/>
@@ -5122,6 +5493,12 @@
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A78:E78"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5142,7 +5519,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -5151,13 +5528,13 @@
     </row>
     <row r="3" ht="14" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5179,13 +5556,13 @@
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B6" s="33" t="s">
         <v>101</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="D6" s="34">
         <f>=100</f>
@@ -5203,7 +5580,7 @@
         <v>101</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="D7" s="34">
         <f>=100</f>
@@ -5215,20 +5592,20 @@
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D8" s="34">
         <f>=100</f>
         <v>100</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5236,17 +5613,17 @@
         <v>82</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D9" s="34">
         <f>=100</f>
         <v>100</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5254,7 +5631,7 @@
         <v>92</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="C10" s="33" t="s">
         <v>72</v>
@@ -5264,7 +5641,7 @@
         <v>100</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5272,7 +5649,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="C12" t="s">
         <v>1</v>
@@ -5310,7 +5687,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="38"/>
@@ -5324,24 +5701,24 @@
         <v>1</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>59</v>
@@ -5355,60 +5732,60 @@
         <v>1</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="C6" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F6" s="34">
         <f>=IF(AND(D6="NOVA",E6="PRESENCIAL"),25,IF(AND(D6="FUP",E6="PRESENCIAL"),10,IF(D6="NOVA",10,IF(D6="FUP",5,0))))</f>
         <v>10</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="C7" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F7" s="34">
         <f>=IF(AND(D7="NOVA",E7="PRESENCIAL"),25,IF(AND(D7="FUP",E7="PRESENCIAL"),10,IF(D7="NOVA",10,IF(D7="FUP",5,0))))</f>
         <v>10</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="B8" s="33" t="s">
         <v>75</v>
@@ -5417,10 +5794,10 @@
         <v>1</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F8" s="34">
         <f>=IF(AND(D8="NOVA",E8="PRESENCIAL"),25,IF(AND(D8="FUP",E8="PRESENCIAL"),10,IF(D8="NOVA",10,IF(D8="FUP",5,0))))</f>
@@ -5441,10 +5818,10 @@
         <v>1</v>
       </c>
       <c r="D9" s="41" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="E9" s="41" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F9" s="42">
         <f>=IF(AND(D9="NOVA",E9="PRESENCIAL"),25,IF(AND(D9="FUP",E9="PRESENCIAL"),10,IF(D9="NOVA",10,IF(D9="FUP",5,0))))</f>
@@ -5459,23 +5836,23 @@
         <v>78</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="C10" s="40" t="s">
         <v>1</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="E10" s="41" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="F10" s="42">
         <f>=IF(AND(D10="NOVA",E10="PRESENCIAL"),25,IF(AND(D10="FUP",E10="PRESENCIAL"),10,IF(D10="NOVA",10,IF(D10="FUP",5,0))))</f>
         <v>10</v>
       </c>
       <c r="G10" s="40" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5486,13 +5863,13 @@
         <v>75</v>
       </c>
       <c r="C11" s="40" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="D11" s="41" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="E11" s="41" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F11" s="42">
         <f>=IF(AND(D11="NOVA",E11="PRESENCIAL"),25,IF(AND(D11="FUP",E11="PRESENCIAL"),10,IF(D11="NOVA",10,IF(D11="FUP",5,0))))</f>
@@ -5507,13 +5884,13 @@
         <v>1</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="C13" t="s">
         <v>1</v>
       </c>
       <c r="D13" s="43" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="E13" t="s">
         <v>1</v>
@@ -5562,7 +5939,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="38"/>
@@ -5576,24 +5953,24 @@
         <v>1</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>59</v>
@@ -5607,55 +5984,55 @@
         <v>1</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
-        <v>154</v>
+        <v>118</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="C6" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F6" s="34">
         <f>=IF(AND(D6="NOVA",E6="PRESENCIAL"),15,IF(AND(D6="FUP",E6="PRESENCIAL"),7.5,IF(D6="NOVA",7.5,IF(D6="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="C7" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F7" s="34">
         <f>=IF(AND(D7="NOVA",E7="PRESENCIAL"),15,IF(AND(D7="FUP",E7="PRESENCIAL"),7.5,IF(D7="NOVA",7.5,IF(D7="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5663,13 +6040,13 @@
         <v>1</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="C9" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="43" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="E9" t="s">
         <v>1</v>
@@ -5712,7 +6089,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="38"/>
@@ -5726,24 +6103,24 @@
         <v>1</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>59</v>
@@ -5757,7 +6134,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5765,47 +6142,47 @@
         <v>70</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="C6" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F6" s="34">
         <f>=IF(AND(D6="NOVA",E6="PRESENCIAL"),15,IF(AND(D6="FUP",E6="PRESENCIAL"),7.5,IF(D6="NOVA",7.5,IF(D6="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="C7" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F7" s="34">
         <f>=IF(AND(D7="NOVA",E7="PRESENCIAL"),15,IF(AND(D7="FUP",E7="PRESENCIAL"),7.5,IF(D7="NOVA",7.5,IF(D7="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5813,47 +6190,47 @@
         <v>88</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="C8" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F8" s="34">
         <f>=IF(AND(D8="NOVA",E8="PRESENCIAL"),15,IF(AND(D8="FUP",E8="PRESENCIAL"),7.5,IF(D8="NOVA",7.5,IF(D8="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="33" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="C9" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F9" s="34">
         <f>=IF(AND(D9="NOVA",E9="PRESENCIAL"),15,IF(AND(D9="FUP",E9="PRESENCIAL"),7.5,IF(D9="NOVA",7.5,IF(D9="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5861,47 +6238,47 @@
         <v>82</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="C10" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F10" s="34">
         <f>=IF(AND(D10="NOVA",E10="PRESENCIAL"),15,IF(AND(D10="FUP",E10="PRESENCIAL"),7.5,IF(D10="NOVA",7.5,IF(D10="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G10" s="33" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="C11" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F11" s="34">
         <f>=IF(AND(D11="NOVA",E11="PRESENCIAL"),15,IF(AND(D11="FUP",E11="PRESENCIAL"),7.5,IF(D11="NOVA",7.5,IF(D11="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5909,23 +6286,23 @@
         <v>65</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="C12" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F12" s="34">
         <f>=IF(AND(D12="NOVA",E12="PRESENCIAL"),15,IF(AND(D12="FUP",E12="PRESENCIAL"),7.5,IF(D12="NOVA",7.5,IF(D12="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G12" s="33" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5933,71 +6310,71 @@
         <v>65</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="C13" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F13" s="34">
         <f>=IF(AND(D13="NOVA",E13="PRESENCIAL"),15,IF(AND(D13="FUP",E13="PRESENCIAL"),7.5,IF(D13="NOVA",7.5,IF(D13="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G13" s="33" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="C14" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F14" s="34">
         <f>=IF(AND(D14="NOVA",E14="PRESENCIAL"),15,IF(AND(D14="FUP",E14="PRESENCIAL"),7.5,IF(D14="NOVA",7.5,IF(D14="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="33" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="C15" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F15" s="34">
         <f>=IF(AND(D15="NOVA",E15="PRESENCIAL"),15,IF(AND(D15="FUP",E15="PRESENCIAL"),7.5,IF(D15="NOVA",7.5,IF(D15="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G15" s="33" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6005,23 +6382,23 @@
         <v>61</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="C16" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F16" s="34">
         <f>=IF(AND(D16="NOVA",E16="PRESENCIAL"),15,IF(AND(D16="FUP",E16="PRESENCIAL"),7.5,IF(D16="NOVA",7.5,IF(D16="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G16" s="33" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6029,23 +6406,23 @@
         <v>61</v>
       </c>
       <c r="B17" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="C17" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="41" t="s">
         <v>163</v>
       </c>
-      <c r="C17" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="D17" s="41" t="s">
-        <v>147</v>
-      </c>
       <c r="E17" s="41" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F17" s="42">
         <f>=IF(AND(D17="NOVA",E17="PRESENCIAL"),15,IF(AND(D17="FUP",E17="PRESENCIAL"),7.5,IF(D17="NOVA",7.5,IF(D17="FUP",5,0))))</f>
         <v>5</v>
       </c>
       <c r="G17" s="40" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6053,47 +6430,47 @@
         <v>61</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="C18" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F18" s="34">
         <f>=IF(AND(D18="NOVA",E18="PRESENCIAL"),15,IF(AND(D18="FUP",E18="PRESENCIAL"),7.5,IF(D18="NOVA",7.5,IF(D18="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G18" s="33" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="33" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="C19" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F19" s="34">
         <f>=IF(AND(D19="NOVA",E19="PRESENCIAL"),15,IF(AND(D19="FUP",E19="PRESENCIAL"),7.5,IF(D19="NOVA",7.5,IF(D19="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G19" s="33" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -6101,13 +6478,13 @@
         <v>1</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="C21" t="s">
         <v>1</v>
       </c>
       <c r="D21" s="43" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="E21" t="s">
         <v>1</v>
@@ -6156,7 +6533,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="38"/>
@@ -6170,24 +6547,24 @@
         <v>1</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>59</v>
@@ -6201,7 +6578,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6209,23 +6586,23 @@
         <v>70</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="C6" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F6" s="34">
         <f>=IF(AND(D6="NOVA",E6="PRESENCIAL"),15,IF(AND(D6="FUP",E6="PRESENCIAL"),7.5,IF(D6="NOVA",7.5,IF(D6="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6233,71 +6610,71 @@
         <v>88</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C7" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F7" s="34">
         <f>=IF(AND(D7="NOVA",E7="PRESENCIAL"),15,IF(AND(D7="FUP",E7="PRESENCIAL"),7.5,IF(D7="NOVA",7.5,IF(D7="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="C8" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F8" s="34">
         <f>=IF(AND(D8="NOVA",E8="PRESENCIAL"),15,IF(AND(D8="FUP",E8="PRESENCIAL"),7.5,IF(D8="NOVA",7.5,IF(D8="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="33" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="C9" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F9" s="34">
         <f>=IF(AND(D9="NOVA",E9="PRESENCIAL"),15,IF(AND(D9="FUP",E9="PRESENCIAL"),7.5,IF(D9="NOVA",7.5,IF(D9="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6305,23 +6682,23 @@
         <v>78</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="C10" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F10" s="34">
         <f>=IF(AND(D10="NOVA",E10="PRESENCIAL"),15,IF(AND(D10="FUP",E10="PRESENCIAL"),7.5,IF(D10="NOVA",7.5,IF(D10="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G10" s="33" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6329,119 +6706,119 @@
         <v>82</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="C11" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F11" s="34">
         <f>=IF(AND(D11="NOVA",E11="PRESENCIAL"),15,IF(AND(D11="FUP",E11="PRESENCIAL"),7.5,IF(D11="NOVA",7.5,IF(D11="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="33" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="C12" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F12" s="34">
         <f>=IF(AND(D12="NOVA",E12="PRESENCIAL"),15,IF(AND(D12="FUP",E12="PRESENCIAL"),7.5,IF(D12="NOVA",7.5,IF(D12="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G12" s="33" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="33" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="C13" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F13" s="34">
         <f>=IF(AND(D13="NOVA",E13="PRESENCIAL"),15,IF(AND(D13="FUP",E13="PRESENCIAL"),7.5,IF(D13="NOVA",7.5,IF(D13="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G13" s="33" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="C14" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F14" s="34">
         <f>=IF(AND(D14="NOVA",E14="PRESENCIAL"),15,IF(AND(D14="FUP",E14="PRESENCIAL"),7.5,IF(D14="NOVA",7.5,IF(D14="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="33" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="C15" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F15" s="34">
         <f>=IF(AND(D15="NOVA",E15="PRESENCIAL"),15,IF(AND(D15="FUP",E15="PRESENCIAL"),7.5,IF(D15="NOVA",7.5,IF(D15="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G15" s="33" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6449,23 +6826,23 @@
         <v>65</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="C16" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F16" s="34">
         <f>=IF(AND(D16="NOVA",E16="PRESENCIAL"),15,IF(AND(D16="FUP",E16="PRESENCIAL"),7.5,IF(D16="NOVA",7.5,IF(D16="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G16" s="33" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6473,47 +6850,47 @@
         <v>65</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="C17" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E17" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F17" s="34">
         <f>=IF(AND(D17="NOVA",E17="PRESENCIAL"),15,IF(AND(D17="FUP",E17="PRESENCIAL"),7.5,IF(D17="NOVA",7.5,IF(D17="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G17" s="33" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="33" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="C18" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F18" s="34">
         <f>=IF(AND(D18="NOVA",E18="PRESENCIAL"),15,IF(AND(D18="FUP",E18="PRESENCIAL"),7.5,IF(D18="NOVA",7.5,IF(D18="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G18" s="33" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6521,23 +6898,23 @@
         <v>61</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="C19" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F19" s="34">
         <f>=IF(AND(D19="NOVA",E19="PRESENCIAL"),15,IF(AND(D19="FUP",E19="PRESENCIAL"),7.5,IF(D19="NOVA",7.5,IF(D19="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G19" s="33" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -6545,13 +6922,13 @@
         <v>1</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="C21" t="s">
         <v>1</v>
       </c>
       <c r="D21" s="43" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="E21" t="s">
         <v>1</v>
@@ -6600,7 +6977,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="38"/>
@@ -6614,24 +6991,24 @@
         <v>1</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>59</v>
@@ -6645,55 +7022,55 @@
         <v>1</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="C6" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F6" s="34">
         <f>=IF(AND(D6="NOVA",E6="PRESENCIAL"),15,IF(AND(D6="FUP",E6="PRESENCIAL"),7.5,IF(D6="NOVA",7.5,IF(D6="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="C7" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F7" s="34">
         <f>=IF(AND(D7="NOVA",E7="PRESENCIAL"),15,IF(AND(D7="FUP",E7="PRESENCIAL"),7.5,IF(D7="NOVA",7.5,IF(D7="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -6701,13 +7078,13 @@
         <v>1</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="C9" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="43" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="E9" t="s">
         <v>1</v>
@@ -6750,7 +7127,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="38"/>
@@ -6764,24 +7141,24 @@
         <v>1</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>59</v>
@@ -6795,7 +7172,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6803,23 +7180,23 @@
         <v>70</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="C6" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F6" s="34">
         <f>=IF(AND(D6="NOVA",E6="PRESENCIAL"),15,IF(AND(D6="FUP",E6="PRESENCIAL"),7.5,IF(D6="NOVA",7.5,IF(D6="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6827,23 +7204,23 @@
         <v>70</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="C7" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F7" s="34">
         <f>=IF(AND(D7="NOVA",E7="PRESENCIAL"),15,IF(AND(D7="FUP",E7="PRESENCIAL"),7.5,IF(D7="NOVA",7.5,IF(D7="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6851,23 +7228,23 @@
         <v>70</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="C8" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F8" s="34">
         <f>=IF(AND(D8="NOVA",E8="PRESENCIAL"),15,IF(AND(D8="FUP",E8="PRESENCIAL"),7.5,IF(D8="NOVA",7.5,IF(D8="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6875,23 +7252,23 @@
         <v>92</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="C9" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F9" s="34">
         <f>=IF(AND(D9="NOVA",E9="PRESENCIAL"),15,IF(AND(D9="FUP",E9="PRESENCIAL"),7.5,IF(D9="NOVA",7.5,IF(D9="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6899,23 +7276,23 @@
         <v>88</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="C10" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F10" s="34">
         <f>=IF(AND(D10="NOVA",E10="PRESENCIAL"),15,IF(AND(D10="FUP",E10="PRESENCIAL"),7.5,IF(D10="NOVA",7.5,IF(D10="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G10" s="33" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6923,23 +7300,23 @@
         <v>88</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="C11" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F11" s="34">
         <f>=IF(AND(D11="NOVA",E11="PRESENCIAL"),15,IF(AND(D11="FUP",E11="PRESENCIAL"),7.5,IF(D11="NOVA",7.5,IF(D11="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6947,23 +7324,23 @@
         <v>74</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="C12" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F12" s="34">
         <f>=IF(AND(D12="NOVA",E12="PRESENCIAL"),15,IF(AND(D12="FUP",E12="PRESENCIAL"),7.5,IF(D12="NOVA",7.5,IF(D12="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G12" s="33" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6971,124 +7348,124 @@
         <v>74</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="C13" s="40" t="s">
         <v>1</v>
       </c>
       <c r="D13" s="41" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="E13" s="41" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F13" s="42">
         <f>=IF(AND(D13="NOVA",E13="PRESENCIAL"),15,IF(AND(D13="FUP",E13="PRESENCIAL"),7.5,IF(D13="NOVA",7.5,IF(D13="FUP",5,0))))</f>
         <v>5</v>
       </c>
       <c r="G13" s="40" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="C14" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F14" s="34">
         <f>=IF(AND(D14="NOVA",E14="PRESENCIAL"),15,IF(AND(D14="FUP",E14="PRESENCIAL"),7.5,IF(D14="NOVA",7.5,IF(D14="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="33" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="C15" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F15" s="34">
         <f>=IF(AND(D15="NOVA",E15="PRESENCIAL"),15,IF(AND(D15="FUP",E15="PRESENCIAL"),7.5,IF(D15="NOVA",7.5,IF(D15="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G15" s="33" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="33" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="C16" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F16" s="34">
         <f>=IF(AND(D16="NOVA",E16="PRESENCIAL"),15,IF(AND(D16="FUP",E16="PRESENCIAL"),7.5,IF(D16="NOVA",7.5,IF(D16="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G16" s="33" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="33" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="C17" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E17" s="32" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F17" s="34">
         <f>=IF(AND(D17="NOVA",E17="PRESENCIAL"),15,IF(AND(D17="FUP",E17="PRESENCIAL"),7.5,IF(D17="NOVA",7.5,IF(D17="FUP",5,0))))</f>
         <v>7.5</v>
       </c>
       <c r="G17" s="33" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="40" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="B18" s="40" t="s">
         <v>1</v>
@@ -7097,10 +7474,10 @@
         <v>1</v>
       </c>
       <c r="D18" s="41" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="F18" s="42">
         <f>=IF(AND(D18="NOVA",E18="PRESENCIAL"),15,IF(AND(D18="FUP",E18="PRESENCIAL"),7.5,IF(D18="NOVA",7.5,IF(D18="FUP",5,0))))</f>
@@ -7115,13 +7492,13 @@
         <v>1</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="C20" t="s">
         <v>1</v>
       </c>
       <c r="D20" s="43" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="E20" t="s">
         <v>1</v>
